--- a/Assets/Document/云熹约定项目文档/9.特殊剧情配置表/周杉/xlsx/周杉事件二.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.特殊剧情配置表/周杉/xlsx/周杉事件二.xlsx
@@ -1,179 +1,628 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="142">
+  <si>
+    <t>角色编号</t>
+  </si>
+  <si>
+    <t>台词编号</t>
+  </si>
+  <si>
+    <t>台词/旁白文本</t>
+  </si>
+  <si>
+    <t>立绘/动作提示</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>凌晨两点十七分，你蜷缩在出租车的后座，手捂着胃，指节因为用力而泛白</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>窗外的城市灯火在雨幕里晕成一片模糊的光斑，像一幅被水浸泡过的油画</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>是急性肠胃炎，连续三天的外卖、两杯冰美式、加上今天下午那顿辣到胃痉挛的火锅，报应来得很快</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>你不想麻烦许映月，她在赶一个项目deadline，已经连续加班三天了，你知道她现在需要睡眠</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>急诊走廊比白天安静了一些，但依然不是那种让人安宁的安静</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>有人在低声哭泣，有人在对护士发脾气，有担架车从你身边推过，轮子摩擦地面发出刺耳的声响</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>消毒水的味道混着某种说不清的药味，在空气里弥漫</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>你坐在金属椅上，手背上扎着针，输液管里的液体一滴一滴地往下坠</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>你掏出手机，划开屏幕，手指在屏幕上漫无目的地滑动，你需要一点白噪音来转移注意力，压制胃部还在持续发作的痉挛</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>然后你鬼使神差般点开了那个陪玩App，在那天之后，你又断断续续点过时安几次，不过多数时候是为了调研</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>你的视线落在关注列表里，那个纯黑色的头像，右下角挂着一个绿色的小点，在线且空闲的标志</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>你想了想，打开交易商城，给他发去了一个小礼物，金额不大，刚好够吸引他的注意力</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>几乎瞬间，他就发来了连麦邀请</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>你连上蓝牙，把耳机塞进耳朵里。走廊里的嘈杂被隔绝了一层，但依然能听见</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>然后，一道带着淡淡倦意的男声，轻轻落进耳里</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>是那种特有的、带着一点沙哑和慵懒的声音，像是本来准备下线了，却被你的提示音拉了回来</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>“老板晚上好，今天是想玩游戏，还是想随便聊聊天？”</t>
+  </si>
+  <si>
+    <t>0000</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>就在他话音落下的瞬间，一辆换药车从你面前经过</t>
+  </si>
+  <si>
+    <t>019</t>
+  </si>
+  <si>
+    <t>金属托盘上摆满了药瓶和器械，轮子碾过地面，托盘碰撞发出清脆声响。紧接着，急诊室的叫号系统也响了</t>
+  </si>
+  <si>
+    <t>020</t>
+  </si>
+  <si>
+    <t>这些声音，顺着你的麦克风，毫无保留地传了过去。你看见通话界面上的音量条跳动了一下，然后，电话那头突然安静了</t>
+  </si>
+  <si>
+    <t>021</t>
+  </si>
+  <si>
+    <t>大概停顿了三四秒，他的声音才再次传来。这一次，他的语速慢了半拍，尾音泄露了一丝不易察觉的紧绷</t>
+  </si>
+  <si>
+    <t>022</t>
+  </si>
+  <si>
+    <t>“老板，你那边的背景音……你在医院？”</t>
+  </si>
+  <si>
+    <t>023</t>
+  </si>
+  <si>
+    <t>你有些疲惫地靠在金属椅背上，你淡淡地“嗯”了一声</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>024</t>
+  </si>
+  <si>
+    <t>“急性肠胃炎，在挂水，没什么大事。”</t>
+  </si>
+  <si>
+    <t>025</t>
+  </si>
+  <si>
+    <t>你的语气很平静，像是在陈述一个和自己无关的事实</t>
+  </si>
+  <si>
+    <t>026</t>
+  </si>
+  <si>
+    <t>听筒里先是传来一声极轻的叹息，然后是一阵翻找东西的窸窣声，像是手在桌面上摸索，在找什么</t>
+  </si>
+  <si>
+    <t>027</t>
+  </si>
+  <si>
+    <t>“既然在输液，就别盯着手机屏幕看了，伤神。”</t>
+  </si>
+  <si>
+    <t>028</t>
+  </si>
+  <si>
+    <t>他的声音变了，褪去了那种刻意保持轻快的陪玩腔调，是一种更加沉稳和缓的真实男声</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>闭上眼睛。如果不舒服，随时打断我。</t>
+  </si>
+  <si>
+    <t>030</t>
+  </si>
+  <si>
+    <t>你犹豫了一下，然后闭上了眼睛，耳机里传来翻书的声音。纸张摩擦的沙沙声，在凌晨的寂静里格外清晰</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>他的声音变成了一种更适合深夜的频段，没有刻意的嘘寒问暖，没有多余的关心和问候</t>
+  </si>
+  <si>
+    <t>032</t>
+  </si>
+  <si>
+    <t>只是用那平稳的嗓音，为你构建了一个隔绝医院喧嚣的听觉屏障</t>
+  </si>
+  <si>
+    <t>033</t>
+  </si>
+  <si>
+    <t>走廊里那些刺耳叫号声、哭声、担架车的声音都变成了遥远的背景音，被他的声音隔绝在另一个世界里</t>
+  </si>
+  <si>
+    <t>034</t>
+  </si>
+  <si>
+    <t>你微微挑眉，你的职业本能让你在放松的状态下依然保持着一丝观察者的清醒</t>
+  </si>
+  <si>
+    <t>035</t>
+  </si>
+  <si>
+    <t>你敏锐地捕捉到了他这场服务中，那一瞬间产生的裂痕</t>
+  </si>
+  <si>
+    <t>036</t>
+  </si>
+  <si>
+    <t>比起像毫无破绽的时安，这个会因为突发状况而泄露一丝真实情绪的年轻人，似乎更生动，也更有意思了一些</t>
+  </si>
+  <si>
+    <t>037</t>
+  </si>
+  <si>
+    <t>他的声音继续在耳边流淌，你听不清他念的是什么内容，可能是散文、小说，或者只是一本他不知道从哪里翻出来的书</t>
+  </si>
+  <si>
+    <t>038</t>
+  </si>
+  <si>
+    <t>你的呼吸慢慢平稳下来，胃部的痉挛似乎也缓解了一些</t>
+  </si>
+  <si>
+    <t>039</t>
+  </si>
+  <si>
+    <t>也许是药效上来了，也许是被他的声音安抚了。你的意识开始变得模糊，像是站在清醒和睡眠的边界线上，摇摇欲坠</t>
+  </si>
+  <si>
+    <t>040</t>
+  </si>
+  <si>
+    <t>不知道过了多久，直到你感觉到手背上的输液管被护士拔掉，你才猛地睁开眼睛，药液见底了</t>
+  </si>
+  <si>
+    <t>041</t>
+  </si>
+  <si>
+    <t>你低头看了一眼手机，通话还在继续，通话时长显示：47分钟</t>
+  </si>
+  <si>
+    <t>042</t>
+  </si>
+  <si>
+    <t>耳机里，他的声音还在继续。已经念到了不知道第几页，声音比刚开始时更低了，带着一丝沙哑，但依然平稳</t>
+  </si>
+  <si>
+    <t>043</t>
+  </si>
+  <si>
+    <t>【抉择选项】为特殊的陪伴买单</t>
+  </si>
+  <si>
+    <t>044</t>
+  </si>
+  <si>
+    <t>你深知在这个世界上，免费的、带有私人情绪的关心才是最昂贵的，必须干脆利落地划清界限</t>
+  </si>
+  <si>
+    <t>045</t>
+  </si>
+  <si>
+    <t>“输液结束了，很感谢你今晚的陪伴。我会按平台最高时薪的双倍结算给你，去睡吧，辛苦了。”</t>
+  </si>
+  <si>
+    <t>046</t>
+  </si>
+  <si>
+    <t>你轻巧地将他这份带有私人情感的陪伴，重新框定在了金钱交易的边界内</t>
+  </si>
+  <si>
+    <t>047</t>
+  </si>
+  <si>
+    <t>你听见他轻轻地吸了一口气，很轻，轻到几乎听不见，但你还是捕捉到了</t>
+  </si>
+  <si>
+    <t>048</t>
+  </si>
+  <si>
+    <t>“……拿钱办事是应该的，老板不用算得这么清楚。既然输完液了，就早点回去休息吧。”</t>
+  </si>
+  <si>
+    <t>049</t>
+  </si>
+  <si>
+    <t>他没有推辞，只是用一句不用算得这么清楚，轻轻地、不着痕迹地，表达了一点点……遗憾？</t>
+  </si>
+  <si>
+    <t>050</t>
+  </si>
+  <si>
+    <t>你听不出来，也许只是你的过度解读</t>
+  </si>
+  <si>
+    <t>051</t>
+  </si>
+  <si>
+    <t>你退出通话，打开交易页面，按你说的数字转了账，备注栏你写的是：服务费，含夜间附加</t>
+  </si>
+  <si>
+    <t>052</t>
+  </si>
+  <si>
+    <t>没有牵绊，没有亏欠，只有清清楚楚的交易，安安全全的距离</t>
+  </si>
+  <si>
+    <t>053</t>
+  </si>
+  <si>
+    <t>【抉择选项】感谢他的陪伴</t>
+  </si>
+  <si>
+    <t>054</t>
+  </si>
+  <si>
+    <t>你看着已经空掉的输液瓶，胃部的痉挛已经平息</t>
+  </si>
+  <si>
+    <t>055</t>
+  </si>
+  <si>
+    <t>护士帮你拔了针，在手背上贴了一小块胶布。你活动了一下手指，血液重新流通的感觉有点麻</t>
+  </si>
+  <si>
+    <t>056</t>
+  </si>
+  <si>
+    <t>你向来习惯一个人扛下所有，也深知虚拟网络与现实的安全界限。但此刻，你愿意给予他这份笨拙的善意一点正向的反馈</t>
+  </si>
+  <si>
+    <t>057</t>
+  </si>
+  <si>
+    <t>“谢谢你刚才的陪伴，你的声音真的是很好的止痛剂。”</t>
+  </si>
+  <si>
+    <t>058</t>
+  </si>
+  <si>
+    <t>这是实话，不是客套也不是恭维。刚才那四十七分钟里，他的声音确实比任何止痛药都有效</t>
+  </si>
+  <si>
+    <t>059</t>
+  </si>
+  <si>
+    <t>“能起作用就好……那我就不打扰老板休息了。回去的路上注意安全，如果可以的话，到家给我发个消息，好吗？”</t>
+  </si>
+  <si>
+    <t>060</t>
+  </si>
+  <si>
+    <t>他最后那个“好吗”说得很轻，像是在问一个很重要的问题，又像是在给自己留一条退路</t>
+  </si>
+  <si>
+    <t>061</t>
+  </si>
+  <si>
+    <t>你还没来得及应声，他又像是怕太过唐突，低声补了一句</t>
+  </si>
+  <si>
+    <t>062</t>
+  </si>
+  <si>
+    <t>“我……只是有点放心不下。”</t>
+  </si>
+  <si>
+    <t>063</t>
+  </si>
+  <si>
+    <t>通话在一片安静又温柔的氛围里结束，你按了挂断键，把手机放进包里</t>
+  </si>
+  <si>
+    <t>064</t>
+  </si>
+  <si>
+    <t>出租车来了。你坐进去，报上地址。车子停下时，你打开和时安的聊天框，打了一行字</t>
+  </si>
+  <si>
+    <t>065</t>
+  </si>
+  <si>
+    <t>“到家了，晚安。”</t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
+    <t>他的回复来得很快，是条语音，带着因困倦带来的沙哑</t>
+  </si>
+  <si>
+    <t>067</t>
+  </si>
+  <si>
+    <t>“老板晚安，好梦。”</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -473,156 +922,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -678,74 +1130,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -997,43 +1386,831 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D68"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="110.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>